--- a/CHI TIET XA NO NSNN.xlsx
+++ b/CHI TIET XA NO NSNN.xlsx
@@ -2876,12 +2876,12 @@
     <col min="1" max="1" width="4.21875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="16.5546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11.44140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.44140625" customWidth="1"/>
+    <col min="4" max="4" width="15.21875" customWidth="1"/>
     <col min="5" max="5" width="16.44140625" customWidth="1"/>
     <col min="6" max="6" width="14" customWidth="1"/>
     <col min="7" max="7" width="13.44140625" customWidth="1"/>
     <col min="8" max="8" width="14.109375" customWidth="1"/>
-    <col min="9" max="9" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.5546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="40.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
@@ -2954,7 +2954,7 @@
         <v>34</v>
       </c>
       <c r="C4" s="27">
-        <v>66138300</v>
+        <v>0</v>
       </c>
       <c r="D4" s="27"/>
       <c r="E4" s="27"/>
@@ -2963,7 +2963,7 @@
       <c r="H4" s="27"/>
       <c r="I4" s="28">
         <f t="shared" ref="I4:I9" si="0">C4+D4+E4+F4+G4+H4</f>
-        <v>66138300</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
@@ -3036,14 +3036,16 @@
       <c r="C8" s="30">
         <v>0</v>
       </c>
-      <c r="D8" s="30"/>
+      <c r="D8" s="14">
+        <v>173376900</v>
+      </c>
       <c r="E8" s="30"/>
       <c r="F8" s="30"/>
       <c r="G8" s="30"/>
       <c r="H8" s="30"/>
       <c r="I8" s="28">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>173376900</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
@@ -3071,16 +3073,31 @@
       <c r="B10" s="36"/>
       <c r="C10" s="31">
         <f>SUM(C3:C9)</f>
-        <v>66138300</v>
-      </c>
-      <c r="D10" s="31"/>
-      <c r="E10" s="31"/>
-      <c r="F10" s="31"/>
-      <c r="G10" s="31"/>
-      <c r="H10" s="31"/>
+        <v>0</v>
+      </c>
+      <c r="D10" s="31">
+        <f t="shared" ref="D10:H10" si="1">SUM(D3:D9)</f>
+        <v>173376900</v>
+      </c>
+      <c r="E10" s="31">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F10" s="31">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G10" s="31">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H10" s="31">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="I10" s="28">
         <f>SUM(I3:I9)</f>
-        <v>66138300</v>
+        <v>173376900</v>
       </c>
     </row>
   </sheetData>

--- a/CHI TIET XA NO NSNN.xlsx
+++ b/CHI TIET XA NO NSNN.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8328" firstSheet="2" activeTab="7"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8328" firstSheet="2" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="XÃ CÁI NƯỚC" sheetId="1" r:id="rId1"/>
@@ -111,9 +111,6 @@
     <t>Số tiền tháng 8</t>
   </si>
   <si>
-    <t>Xã/phường</t>
-  </si>
-  <si>
     <t>Tháng 7/2026</t>
   </si>
   <si>
@@ -166,6 +163,9 @@
   </si>
   <si>
     <t>DANH SÁCH NỢ NGÂN SÁCH NHÀ NƯỚC</t>
+  </si>
+  <si>
+    <t>Xã</t>
   </si>
 </sst>
 </file>
@@ -783,16 +783,16 @@
         <v>25</v>
       </c>
       <c r="E2" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="F2" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="F2" s="13" t="s">
+      <c r="G2" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="G2" s="13" t="s">
+      <c r="H2" s="13" t="s">
         <v>42</v>
-      </c>
-      <c r="H2" s="13" t="s">
-        <v>43</v>
       </c>
       <c r="I2" s="13" t="s">
         <v>14</v>
@@ -1134,16 +1134,16 @@
         <v>25</v>
       </c>
       <c r="E2" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="F2" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="F2" s="13" t="s">
+      <c r="G2" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="G2" s="13" t="s">
+      <c r="H2" s="13" t="s">
         <v>42</v>
-      </c>
-      <c r="H2" s="13" t="s">
-        <v>43</v>
       </c>
       <c r="I2" s="13" t="s">
         <v>14</v>
@@ -1449,16 +1449,16 @@
         <v>25</v>
       </c>
       <c r="E2" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="F2" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="F2" s="13" t="s">
+      <c r="G2" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="G2" s="13" t="s">
+      <c r="H2" s="13" t="s">
         <v>42</v>
-      </c>
-      <c r="H2" s="13" t="s">
-        <v>43</v>
       </c>
       <c r="I2" s="13" t="s">
         <v>14</v>
@@ -1763,16 +1763,16 @@
         <v>25</v>
       </c>
       <c r="E2" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="F2" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="F2" s="13" t="s">
+      <c r="G2" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="G2" s="13" t="s">
+      <c r="H2" s="13" t="s">
         <v>42</v>
-      </c>
-      <c r="H2" s="13" t="s">
-        <v>43</v>
       </c>
       <c r="I2" s="13" t="s">
         <v>14</v>
@@ -2078,16 +2078,16 @@
         <v>25</v>
       </c>
       <c r="E2" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="F2" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="F2" s="13" t="s">
+      <c r="G2" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="G2" s="13" t="s">
+      <c r="H2" s="13" t="s">
         <v>42</v>
-      </c>
-      <c r="H2" s="13" t="s">
-        <v>43</v>
       </c>
       <c r="I2" s="13" t="s">
         <v>14</v>
@@ -2350,16 +2350,16 @@
         <v>25</v>
       </c>
       <c r="E2" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="F2" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="F2" s="13" t="s">
+      <c r="G2" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="G2" s="13" t="s">
+      <c r="H2" s="13" t="s">
         <v>42</v>
-      </c>
-      <c r="H2" s="13" t="s">
-        <v>43</v>
       </c>
       <c r="I2" s="13" t="s">
         <v>14</v>
@@ -2621,16 +2621,16 @@
         <v>25</v>
       </c>
       <c r="E2" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="F2" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="F2" s="13" t="s">
+      <c r="G2" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="G2" s="13" t="s">
+      <c r="H2" s="13" t="s">
         <v>42</v>
-      </c>
-      <c r="H2" s="13" t="s">
-        <v>43</v>
       </c>
       <c r="I2" s="13" t="s">
         <v>14</v>
@@ -2886,7 +2886,7 @@
   <sheetData>
     <row r="1" spans="1:9" ht="40.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="34" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B1" s="34"/>
       <c r="C1" s="34"/>
@@ -2902,25 +2902,25 @@
         <v>15</v>
       </c>
       <c r="B2" s="24" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2" s="24" t="s">
         <v>26</v>
       </c>
-      <c r="C2" s="24" t="s">
+      <c r="D2" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="D2" s="24" t="s">
+      <c r="E2" s="24" t="s">
         <v>28</v>
       </c>
-      <c r="E2" s="24" t="s">
+      <c r="F2" s="24" t="s">
         <v>29</v>
       </c>
-      <c r="F2" s="24" t="s">
+      <c r="G2" s="24" t="s">
         <v>30</v>
       </c>
-      <c r="G2" s="24" t="s">
+      <c r="H2" s="24" t="s">
         <v>31</v>
-      </c>
-      <c r="H2" s="24" t="s">
-        <v>32</v>
       </c>
       <c r="I2" s="13" t="s">
         <v>14</v>
@@ -2931,7 +2931,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="26" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C3" s="27">
         <v>0</v>
@@ -2951,7 +2951,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="26" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C4" s="27">
         <v>0</v>
@@ -2971,7 +2971,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="26" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C5" s="27">
         <v>0</v>
@@ -2991,7 +2991,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="26" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C6" s="27">
         <v>0</v>
@@ -3011,7 +3011,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="29" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C7" s="30">
         <v>0</v>
@@ -3031,7 +3031,7 @@
         <v>6</v>
       </c>
       <c r="B8" s="29" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C8" s="30">
         <v>0</v>
@@ -3053,7 +3053,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="29" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C9" s="30">
         <v>0</v>
